--- a/Spesenabrechnung_Vorlage.xlsx
+++ b/Spesenabrechnung_Vorlage.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wopi.dropbox.com/wopi/files/oid_11533718751456555520/WOPIServiceId_TP_DROPBOX_PLUS/WOPIUserId_-/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/knausprs/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="8_{5CDD2B8F-DC00-0D47-8623-2CEA972F14E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECDEB46E-EDD6-0D49-871D-961BFA65ABE8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E18E1C1-E726-AF48-8082-C17EE1A0959B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="23240" windowHeight="21540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="23240" windowHeight="19920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spesenabrechnung" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>Spesenabrechnung</t>
   </si>
@@ -133,9 +133,6 @@
   </si>
   <si>
     <t>Belege</t>
-  </si>
-  <si>
-    <t>Benjamin Knaus</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -864,7 +861,7 @@
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="E4" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
@@ -1009,9 +1006,7 @@
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="23" t="s">
-        <v>33</v>
-      </c>
+      <c r="B9" s="23"/>
       <c r="C9" s="23"/>
       <c r="D9" s="24"/>
       <c r="E9" s="8"/>
@@ -30961,26 +30956,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="36b76a7a-2cfe-4bac-aaac-2427a978a688" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f3cf4560-e8c0-4c72-b8c7-31f62c9d5852">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100DCFDAC16AC7ED9468437DFE26886DEF0" ma:contentTypeVersion="18" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="f1bd32f2f57cf897fd9a3984331b27f1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="36b76a7a-2cfe-4bac-aaac-2427a978a688" xmlns:ns3="f3cf4560-e8c0-4c72-b8c7-31f62c9d5852" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce7032b24bf91d1e2256b5870300a519" ns2:_="" ns3:_="">
     <xsd:import namespace="36b76a7a-2cfe-4bac-aaac-2427a978a688"/>
@@ -31235,10 +31210,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="36b76a7a-2cfe-4bac-aaac-2427a978a688" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f3cf4560-e8c0-4c72-b8c7-31f62c9d5852">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A95DB93-ABBB-442B-B349-720DFA7BF598}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0826390A-733F-4CE1-B160-8441DC797764}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="36b76a7a-2cfe-4bac-aaac-2427a978a688"/>
+    <ds:schemaRef ds:uri="f3cf4560-e8c0-4c72-b8c7-31f62c9d5852"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31261,20 +31267,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0826390A-733F-4CE1-B160-8441DC797764}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A95DB93-ABBB-442B-B349-720DFA7BF598}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="36b76a7a-2cfe-4bac-aaac-2427a978a688"/>
-    <ds:schemaRef ds:uri="f3cf4560-e8c0-4c72-b8c7-31f62c9d5852"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>